--- a/RISULTATI DECOUPLED/RISULTATI_decoupledVitBg4SXZ.xlsx
+++ b/RISULTATI DECOUPLED/RISULTATI_decoupledVitBg4SXZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - Politecnico di Milano\Documenti\POLIMI\Tesi\distillation\RISULTATI DECOUPLED\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E98E7C-5EC4-436E-8091-C72C39D9A640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461D62E8-9ADE-4C3A-A6D8-12E1538E0BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{66177380-6D0E-41A8-968E-9FE0E0B69BFF}"/>
+    <workbookView minimized="1" xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{66177380-6D0E-41A8-968E-9FE0E0B69BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio2" sheetId="2" r:id="rId1"/>
@@ -19,8 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Foglio1!$H$6:$H$80</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Foglio1!$J$89</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Foglio1!$Q$5:$Q$79</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Foglio1!$Q$5:$Q$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>MODELLO CMT DISTILLATO</t>
   </si>
@@ -158,6 +157,9 @@
   </si>
   <si>
     <t>H0: LE DUE DISTRIBUZIONI PROVENGONO DALLA STESSA POPOLAZIONE</t>
+  </si>
+  <si>
+    <t>MASCHERE CON REFINING che non viene contato nel conteggio del tmepo</t>
   </si>
 </sst>
 </file>
@@ -282,7 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -295,18 +297,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1092,7 +1091,7 @@
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1130,6 +1129,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{15D0D1F9-4101-4CA3-B2A6-19D430D61380}">
           <cx:tx>
             <cx:txData>
+              <cx:f/>
               <cx:v>student</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1141,6 +1141,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000002-4A99-4979-9281-4CE9C32F1DD6}">
           <cx:tx>
             <cx:txData>
+              <cx:f/>
               <cx:v>sam</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2280,15 +2281,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
+      <xdr:colOff>243840</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>287655</xdr:colOff>
+      <xdr:colOff>386715</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>165383</xdr:rowOff>
+      <xdr:rowOff>153953</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2305,8 +2306,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3190875" y="15240"/>
-          <a:ext cx="1969770" cy="515903"/>
+          <a:off x="3291840" y="0"/>
+          <a:ext cx="1971675" cy="519713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2511,8 +2512,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="21355050" y="7278051"/>
-              <a:ext cx="5164455" cy="3856673"/>
+              <a:off x="21358860" y="7354251"/>
+              <a:ext cx="5164455" cy="3896678"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2990,118 +2991,111 @@
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1"/>
     <row r="3" spans="1:3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4">
         <v>0.81460906991260795</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4">
         <v>0.91146478888225169</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5">
         <v>1.7571746653809717E-3</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5">
         <v>3.8104610247281074E-4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6">
         <v>75</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7">
         <v>1.0691103839268912E-3</v>
       </c>
-      <c r="C7" s="15"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="15"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9">
         <v>148</v>
       </c>
-      <c r="C9" s="15"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10">
         <v>-18.13968032706763</v>
       </c>
-      <c r="C10" s="15"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11">
         <v>9.5538218953756642E-40</v>
       </c>
-      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12">
         <v>1.655214506178732</v>
       </c>
-      <c r="C12" s="15"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13">
         <v>1.9107643790751328E-39</v>
       </c>
-      <c r="C13" s="15"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="13">
         <v>1.9761224936137434</v>
       </c>
-      <c r="C14" s="16"/>
+      <c r="C14" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3129,109 +3123,103 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4">
         <v>0.81460906991260795</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4">
         <v>0.91146189884682749</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5">
         <v>1.7571746653809717E-3</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5">
         <v>3.8118053582184409E-4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6">
         <v>75</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" s="15"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8">
         <v>105</v>
       </c>
-      <c r="C8" s="15"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9">
         <v>-18.138568873671115</v>
       </c>
-      <c r="C9" s="15"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10">
         <v>1.958686601391606E-34</v>
       </c>
-      <c r="C10" s="15"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11">
         <v>1.6594953834068058</v>
       </c>
-      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12">
         <v>3.917373202783212E-34</v>
       </c>
-      <c r="C12" s="15"/>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="13">
         <v>1.9828152737950464</v>
       </c>
-      <c r="C13" s="16"/>
+      <c r="C13" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3257,6 +3245,9 @@
       </c>
     </row>
     <row r="2" spans="1:33">
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
       <c r="S2" s="4" t="s">
         <v>2</v>
       </c>
@@ -3303,24 +3294,24 @@
       <c r="V4" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="11" t="s">
+      <c r="AE4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="AF4" s="11" t="s">
+      <c r="AF4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AG4" s="11" t="s">
+      <c r="AG4" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:33">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -3359,24 +3350,24 @@
       <c r="V5">
         <v>0.91780141282197003</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AE5" s="9">
         <v>518.61095428467002</v>
       </c>
-      <c r="AF5" s="11">
+      <c r="AF5" s="9">
         <v>0</v>
       </c>
-      <c r="AG5" s="11">
+      <c r="AG5" s="9">
         <v>0.84228301249577997</v>
       </c>
     </row>
     <row r="6" spans="1:33">
-      <c r="A6" s="12">
+      <c r="A6" s="9">
         <v>3322.5419521332001</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="9">
         <v>0</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <v>0.70908214067886</v>
       </c>
       <c r="F6" s="9">
@@ -3415,24 +3406,24 @@
       <c r="V6">
         <v>0.91729487301824997</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AE6" s="9">
         <v>102.83994674682999</v>
       </c>
-      <c r="AF6" s="11">
+      <c r="AF6" s="9">
         <v>1</v>
       </c>
-      <c r="AG6" s="11">
+      <c r="AG6" s="9">
         <v>0.75369659442724002</v>
       </c>
     </row>
     <row r="7" spans="1:33">
-      <c r="A7" s="12">
+      <c r="A7" s="9">
         <v>3020.2198028563998</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="9">
         <v>1</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="9">
         <v>0.82241117102171002</v>
       </c>
       <c r="F7" s="9">
@@ -3471,24 +3462,24 @@
       <c r="V7">
         <v>0.92838062030762003</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AE7" s="9">
         <v>103.45911979675</v>
       </c>
-      <c r="AF7" s="11">
+      <c r="AF7" s="9">
         <v>2</v>
       </c>
-      <c r="AG7" s="11">
+      <c r="AG7" s="9">
         <v>0.78620887552555996</v>
       </c>
     </row>
     <row r="8" spans="1:33">
-      <c r="A8" s="12">
+      <c r="A8" s="9">
         <v>3300.5454540252999</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="9">
         <v>2</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="9">
         <v>0.84968493630777997</v>
       </c>
       <c r="F8" s="9">
@@ -3527,24 +3518,24 @@
       <c r="V8">
         <v>0.92154698822556003</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AE8" s="9">
         <v>101.26090049744001</v>
       </c>
-      <c r="AF8" s="11">
+      <c r="AF8" s="9">
         <v>3</v>
       </c>
-      <c r="AG8" s="11">
+      <c r="AG8" s="9">
         <v>0.83693650024236999</v>
       </c>
     </row>
     <row r="9" spans="1:33">
-      <c r="A9" s="12">
+      <c r="A9" s="9">
         <v>3621.1149692535</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="9">
         <v>3</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="9">
         <v>0.83475532341778003</v>
       </c>
       <c r="F9" s="9">
@@ -3583,24 +3574,24 @@
       <c r="V9">
         <v>0.94142830510279996</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AE9" s="9">
         <v>103.7003993988</v>
       </c>
-      <c r="AF9" s="11">
+      <c r="AF9" s="9">
         <v>4</v>
       </c>
-      <c r="AG9" s="11">
+      <c r="AG9" s="9">
         <v>0.84723542761171999</v>
       </c>
     </row>
     <row r="10" spans="1:33">
-      <c r="A10" s="12">
+      <c r="A10" s="9">
         <v>3074.0873813629</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="9">
         <v>4</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9">
         <v>0.86335311971206996</v>
       </c>
       <c r="F10" s="9">
@@ -3639,24 +3630,24 @@
       <c r="V10">
         <v>0.89411425274091005</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AE10" s="9">
         <v>101.51934623718</v>
       </c>
-      <c r="AF10" s="11">
+      <c r="AF10" s="9">
         <v>5</v>
       </c>
-      <c r="AG10" s="11">
+      <c r="AG10" s="9">
         <v>0.85816622931955999</v>
       </c>
     </row>
     <row r="11" spans="1:33">
-      <c r="A11" s="12">
+      <c r="A11" s="9">
         <v>3125.0267028808998</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="9">
         <v>5</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="9">
         <v>0.81735873576324003</v>
       </c>
       <c r="F11" s="9">
@@ -3695,24 +3686,24 @@
       <c r="V11">
         <v>0.92310475583986995</v>
       </c>
-      <c r="AE11" s="11">
+      <c r="AE11" s="9">
         <v>101.37391090393</v>
       </c>
-      <c r="AF11" s="11">
+      <c r="AF11" s="9">
         <v>6</v>
       </c>
-      <c r="AG11" s="11">
+      <c r="AG11" s="9">
         <v>0.71543827386671999</v>
       </c>
     </row>
     <row r="12" spans="1:33">
-      <c r="A12" s="12">
+      <c r="A12" s="9">
         <v>3107.4945926666001</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="9">
         <v>6</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <v>0.84360445238005</v>
       </c>
       <c r="F12" s="9">
@@ -3751,24 +3742,24 @@
       <c r="V12">
         <v>0.91489639193843997</v>
       </c>
-      <c r="AE12" s="11">
+      <c r="AE12" s="9">
         <v>101.52077674866</v>
       </c>
-      <c r="AF12" s="11">
+      <c r="AF12" s="9">
         <v>7</v>
       </c>
-      <c r="AG12" s="11">
+      <c r="AG12" s="9">
         <v>0.86472009548484996</v>
       </c>
     </row>
     <row r="13" spans="1:33">
-      <c r="A13" s="12">
+      <c r="A13" s="9">
         <v>3105.5862903594998</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <v>7</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="9">
         <v>0.78513771926598996</v>
       </c>
       <c r="F13" s="9">
@@ -3807,24 +3798,24 @@
       <c r="V13">
         <v>0.90897005951841003</v>
       </c>
-      <c r="AE13" s="11">
+      <c r="AE13" s="9">
         <v>101.54891014099</v>
       </c>
-      <c r="AF13" s="11">
+      <c r="AF13" s="9">
         <v>8</v>
       </c>
-      <c r="AG13" s="11">
+      <c r="AG13" s="9">
         <v>0.84624020460661997</v>
       </c>
     </row>
     <row r="14" spans="1:33">
-      <c r="A14" s="12">
+      <c r="A14" s="9">
         <v>4318.5739517211996</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="9">
         <v>8</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="9">
         <v>0.80419205249006998</v>
       </c>
       <c r="F14" s="9">
@@ -3863,24 +3854,24 @@
       <c r="V14">
         <v>0.92724374367726003</v>
       </c>
-      <c r="AE14" s="11">
+      <c r="AE14" s="9">
         <v>101.10616683959999</v>
       </c>
-      <c r="AF14" s="11">
+      <c r="AF14" s="9">
         <v>9</v>
       </c>
-      <c r="AG14" s="11">
+      <c r="AG14" s="9">
         <v>0.72472746677509003</v>
       </c>
     </row>
     <row r="15" spans="1:33">
-      <c r="A15" s="12">
+      <c r="A15" s="9">
         <v>4418.0657863616998</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="9">
         <v>9</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="9">
         <v>0.83444771097293002</v>
       </c>
       <c r="F15" s="9">
@@ -3919,24 +3910,24 @@
       <c r="V15">
         <v>0.89961278476607998</v>
       </c>
-      <c r="AE15" s="11">
+      <c r="AE15" s="9">
         <v>103.30748558044</v>
       </c>
-      <c r="AF15" s="11">
+      <c r="AF15" s="9">
         <v>10</v>
       </c>
-      <c r="AG15" s="11">
+      <c r="AG15" s="9">
         <v>0.84460545449906999</v>
       </c>
     </row>
     <row r="16" spans="1:33">
-      <c r="A16" s="12">
+      <c r="A16" s="9">
         <v>4575.4911899566996</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="9">
         <v>10</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="9">
         <v>0.83120529447156</v>
       </c>
       <c r="F16" s="9">
@@ -3975,24 +3966,24 @@
       <c r="V16">
         <v>0.89666380969323001</v>
       </c>
-      <c r="AE16" s="11">
+      <c r="AE16" s="9">
         <v>101.15265846251999</v>
       </c>
-      <c r="AF16" s="11">
+      <c r="AF16" s="9">
         <v>11</v>
       </c>
-      <c r="AG16" s="11">
+      <c r="AG16" s="9">
         <v>0.74957430894826005</v>
       </c>
     </row>
     <row r="17" spans="1:33">
-      <c r="A17" s="12">
+      <c r="A17" s="9">
         <v>4850.4569530486997</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="9">
         <v>11</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="9">
         <v>0.82185876193262997</v>
       </c>
       <c r="F17" s="9">
@@ -4031,24 +4022,24 @@
       <c r="V17">
         <v>0.91097098770121998</v>
       </c>
-      <c r="AE17" s="11">
+      <c r="AE17" s="9">
         <v>98.932504653931005</v>
       </c>
-      <c r="AF17" s="11">
+      <c r="AF17" s="9">
         <v>12</v>
       </c>
-      <c r="AG17" s="11">
+      <c r="AG17" s="9">
         <v>0.84939326939430004</v>
       </c>
     </row>
     <row r="18" spans="1:33">
-      <c r="A18" s="12">
+      <c r="A18" s="9">
         <v>4375.8754730225</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="9">
         <v>12</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="9">
         <v>0.81969892591269999</v>
       </c>
       <c r="F18" s="9">
@@ -4087,24 +4078,24 @@
       <c r="V18">
         <v>0.91831257442022995</v>
       </c>
-      <c r="AE18" s="11">
+      <c r="AE18" s="9">
         <v>101.89652442932</v>
       </c>
-      <c r="AF18" s="11">
+      <c r="AF18" s="9">
         <v>13</v>
       </c>
-      <c r="AG18" s="11">
+      <c r="AG18" s="9">
         <v>0.83030359097706996</v>
       </c>
     </row>
     <row r="19" spans="1:33">
-      <c r="A19" s="12">
+      <c r="A19" s="9">
         <v>3624.5553493500001</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="9">
         <v>13</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="9">
         <v>0.83394996749125005</v>
       </c>
       <c r="F19" s="9">
@@ -4143,24 +4134,24 @@
       <c r="V19">
         <v>0.90529971785437002</v>
       </c>
-      <c r="AE19" s="11">
+      <c r="AE19" s="9">
         <v>103.36732864379999</v>
       </c>
-      <c r="AF19" s="11">
+      <c r="AF19" s="9">
         <v>14</v>
       </c>
-      <c r="AG19" s="11">
+      <c r="AG19" s="9">
         <v>0.83723001392027996</v>
       </c>
     </row>
     <row r="20" spans="1:33">
-      <c r="A20" s="12">
+      <c r="A20" s="9">
         <v>3612.5802993774</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="9">
         <v>14</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="9">
         <v>0.84472016735387001</v>
       </c>
       <c r="F20" s="9">
@@ -4199,24 +4190,24 @@
       <c r="V20">
         <v>0.91567316521594</v>
       </c>
-      <c r="AE20" s="11">
+      <c r="AE20" s="9">
         <v>101.63998603821</v>
       </c>
-      <c r="AF20" s="11">
+      <c r="AF20" s="9">
         <v>15</v>
       </c>
-      <c r="AG20" s="11">
+      <c r="AG20" s="9">
         <v>0.84763070004299002</v>
       </c>
     </row>
     <row r="21" spans="1:33">
-      <c r="A21" s="12">
+      <c r="A21" s="9">
         <v>3708.4474563599001</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="9">
         <v>15</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="9">
         <v>0.82472287116448995</v>
       </c>
       <c r="F21" s="9">
@@ -4255,24 +4246,24 @@
       <c r="V21">
         <v>0.93141616116228998</v>
       </c>
-      <c r="AE21" s="11">
+      <c r="AE21" s="9">
         <v>103.38616371155</v>
       </c>
-      <c r="AF21" s="11">
+      <c r="AF21" s="9">
         <v>16</v>
       </c>
-      <c r="AG21" s="11">
+      <c r="AG21" s="9">
         <v>0.82901979688487004</v>
       </c>
     </row>
     <row r="22" spans="1:33">
-      <c r="A22" s="12">
+      <c r="A22" s="9">
         <v>3456.2025070190002</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="9">
         <v>16</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="9">
         <v>0.77941787808825003</v>
       </c>
       <c r="F22" s="9">
@@ -4311,24 +4302,24 @@
       <c r="V22">
         <v>0.91395767773184999</v>
       </c>
-      <c r="AE22" s="11">
+      <c r="AE22" s="9">
         <v>101.22728347778001</v>
       </c>
-      <c r="AF22" s="11">
+      <c r="AF22" s="9">
         <v>17</v>
       </c>
-      <c r="AG22" s="11">
+      <c r="AG22" s="9">
         <v>0.83005784257349002</v>
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="A23" s="12">
+      <c r="A23" s="9">
         <v>3571.0437297820999</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="9">
         <v>17</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="9">
         <v>0.82381891533836005</v>
       </c>
       <c r="F23" s="9">
@@ -4367,24 +4358,24 @@
       <c r="V23">
         <v>0.92156318932934</v>
       </c>
-      <c r="AE23" s="11">
+      <c r="AE23" s="9">
         <v>103.84368896484</v>
       </c>
-      <c r="AF23" s="11">
+      <c r="AF23" s="9">
         <v>18</v>
       </c>
-      <c r="AG23" s="11">
+      <c r="AG23" s="9">
         <v>0.87318459628677003</v>
       </c>
     </row>
     <row r="24" spans="1:33">
-      <c r="A24" s="12">
+      <c r="A24" s="9">
         <v>3483.0312728882</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="9">
         <v>18</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="9">
         <v>0.84761764272017004</v>
       </c>
       <c r="F24" s="9">
@@ -4423,24 +4414,24 @@
       <c r="V24">
         <v>0.91794417928375005</v>
       </c>
-      <c r="AE24" s="11">
+      <c r="AE24" s="9">
         <v>101.42874717712</v>
       </c>
-      <c r="AF24" s="11">
+      <c r="AF24" s="9">
         <v>19</v>
       </c>
-      <c r="AG24" s="11">
+      <c r="AG24" s="9">
         <v>0.85233456547497</v>
       </c>
     </row>
     <row r="25" spans="1:33">
-      <c r="A25" s="12">
+      <c r="A25" s="9">
         <v>3545.8660125731999</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="9">
         <v>19</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="9">
         <v>0.84728570534092995</v>
       </c>
       <c r="F25" s="9">
@@ -4479,24 +4470,24 @@
       <c r="V25">
         <v>0.90565532848612995</v>
       </c>
-      <c r="AE25" s="11">
+      <c r="AE25" s="9">
         <v>103.32775115967</v>
       </c>
-      <c r="AF25" s="11">
+      <c r="AF25" s="9">
         <v>20</v>
       </c>
-      <c r="AG25" s="11">
+      <c r="AG25" s="9">
         <v>0.83087682645639005</v>
       </c>
     </row>
     <row r="26" spans="1:33">
-      <c r="A26" s="12">
+      <c r="A26" s="9">
         <v>2809.4229698180998</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="9">
         <v>20</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="9">
         <v>0.81149662510784004</v>
       </c>
       <c r="F26" s="9">
@@ -4535,24 +4526,24 @@
       <c r="V26">
         <v>0.91375341095477003</v>
       </c>
-      <c r="AE26" s="11">
+      <c r="AE26" s="9">
         <v>101.50122642517</v>
       </c>
-      <c r="AF26" s="11">
+      <c r="AF26" s="9">
         <v>21</v>
       </c>
-      <c r="AG26" s="11">
+      <c r="AG26" s="9">
         <v>0.85198473975837996</v>
       </c>
     </row>
     <row r="27" spans="1:33">
-      <c r="A27" s="12">
+      <c r="A27" s="9">
         <v>2664.2940044402999</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="9">
         <v>21</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="9">
         <v>0.84785964912280998</v>
       </c>
       <c r="F27" s="9">
@@ -4591,24 +4582,24 @@
       <c r="V27">
         <v>0.92512343655312002</v>
       </c>
-      <c r="AE27" s="11">
+      <c r="AE27" s="9">
         <v>103.40166091918999</v>
       </c>
-      <c r="AF27" s="11">
+      <c r="AF27" s="9">
         <v>22</v>
       </c>
-      <c r="AG27" s="11">
+      <c r="AG27" s="9">
         <v>0.83666426290305995</v>
       </c>
     </row>
     <row r="28" spans="1:33">
-      <c r="A28" s="12">
+      <c r="A28" s="9">
         <v>3210.9725475311002</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="9">
         <v>22</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="9">
         <v>0.84078730967159998</v>
       </c>
       <c r="F28" s="9">
@@ -4647,24 +4638,24 @@
       <c r="V28">
         <v>0.89295034067170997</v>
       </c>
-      <c r="AE28" s="11">
+      <c r="AE28" s="9">
         <v>101.65882110596</v>
       </c>
-      <c r="AF28" s="11">
+      <c r="AF28" s="9">
         <v>23</v>
       </c>
-      <c r="AG28" s="11">
+      <c r="AG28" s="9">
         <v>0.82071835567757001</v>
       </c>
     </row>
     <row r="29" spans="1:33">
-      <c r="A29" s="12">
+      <c r="A29" s="9">
         <v>3130.0494670868002</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="9">
         <v>23</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="9">
         <v>0.70607182987224004</v>
       </c>
       <c r="F29" s="9">
@@ -4703,24 +4694,24 @@
       <c r="V29">
         <v>0.90292459141738002</v>
       </c>
-      <c r="AE29" s="11">
+      <c r="AE29" s="9">
         <v>103.21736335753999</v>
       </c>
-      <c r="AF29" s="11">
+      <c r="AF29" s="9">
         <v>24</v>
       </c>
-      <c r="AG29" s="11">
+      <c r="AG29" s="9">
         <v>0.86668164648440005</v>
       </c>
     </row>
     <row r="30" spans="1:33">
-      <c r="A30" s="12">
+      <c r="A30" s="9">
         <v>3132.2557926178001</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="9">
         <v>24</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="9">
         <v>0.84992618312054002</v>
       </c>
       <c r="F30" s="9">
@@ -4759,24 +4750,24 @@
       <c r="V30">
         <v>0.92217090785110001</v>
       </c>
-      <c r="AE30" s="11">
+      <c r="AE30" s="9">
         <v>101.36890411377</v>
       </c>
-      <c r="AF30" s="11">
+      <c r="AF30" s="9">
         <v>25</v>
       </c>
-      <c r="AG30" s="11">
+      <c r="AG30" s="9">
         <v>0.7381232438084</v>
       </c>
     </row>
     <row r="31" spans="1:33">
-      <c r="A31" s="12">
+      <c r="A31" s="9">
         <v>3168.0953502655002</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="9">
         <v>25</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="9">
         <v>0.82894545898922001</v>
       </c>
       <c r="F31" s="9">
@@ -4815,24 +4806,24 @@
       <c r="V31">
         <v>0.92378429542377005</v>
       </c>
-      <c r="AE31" s="11">
+      <c r="AE31" s="9">
         <v>101.39727592468</v>
       </c>
-      <c r="AF31" s="11">
+      <c r="AF31" s="9">
         <v>26</v>
       </c>
-      <c r="AG31" s="11">
+      <c r="AG31" s="9">
         <v>0.86607258365231998</v>
       </c>
     </row>
     <row r="32" spans="1:33">
-      <c r="A32" s="12">
+      <c r="A32" s="9">
         <v>2890.1507854462002</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="9">
         <v>26</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="9">
         <v>0.83297421509337999</v>
       </c>
       <c r="F32" s="9">
@@ -4871,24 +4862,24 @@
       <c r="V32">
         <v>0.83845038326082</v>
       </c>
-      <c r="AE32" s="11">
+      <c r="AE32" s="9">
         <v>101.70269012451</v>
       </c>
-      <c r="AF32" s="11">
+      <c r="AF32" s="9">
         <v>27</v>
       </c>
-      <c r="AG32" s="11">
+      <c r="AG32" s="9">
         <v>0.87203548546081999</v>
       </c>
     </row>
     <row r="33" spans="1:33">
-      <c r="A33" s="12">
+      <c r="A33" s="9">
         <v>3098.5808372498</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="9">
         <v>27</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="9">
         <v>0.82441062779788998</v>
       </c>
       <c r="F33" s="9">
@@ -4927,24 +4918,24 @@
       <c r="V33">
         <v>0.91478006299186998</v>
       </c>
-      <c r="AE33" s="11">
+      <c r="AE33" s="9">
         <v>103.24215888977</v>
       </c>
-      <c r="AF33" s="11">
+      <c r="AF33" s="9">
         <v>28</v>
       </c>
-      <c r="AG33" s="11">
+      <c r="AG33" s="9">
         <v>0.85711846413114001</v>
       </c>
     </row>
     <row r="34" spans="1:33">
-      <c r="A34" s="12">
+      <c r="A34" s="9">
         <v>2759.2988014221</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="9">
         <v>28</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="9">
         <v>0.83793867950034995</v>
       </c>
       <c r="F34" s="9">
@@ -4983,24 +4974,24 @@
       <c r="V34">
         <v>0.89937106918238996</v>
       </c>
-      <c r="AE34" s="11">
+      <c r="AE34" s="9">
         <v>101.72462463379</v>
       </c>
-      <c r="AF34" s="11">
+      <c r="AF34" s="9">
         <v>29</v>
       </c>
-      <c r="AG34" s="11">
+      <c r="AG34" s="9">
         <v>0.84875618773105999</v>
       </c>
     </row>
     <row r="35" spans="1:33">
-      <c r="A35" s="12">
+      <c r="A35" s="9">
         <v>2724.0684032439999</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="9">
         <v>29</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="9">
         <v>0.74906750946726997</v>
       </c>
       <c r="F35" s="9">
@@ -5039,24 +5030,24 @@
       <c r="V35">
         <v>0.91322623405701997</v>
       </c>
-      <c r="AE35" s="11">
+      <c r="AE35" s="9">
         <v>103.75928878784001</v>
       </c>
-      <c r="AF35" s="11">
+      <c r="AF35" s="9">
         <v>30</v>
       </c>
-      <c r="AG35" s="11">
+      <c r="AG35" s="9">
         <v>0.84604915900359001</v>
       </c>
     </row>
     <row r="36" spans="1:33">
-      <c r="A36" s="12">
+      <c r="A36" s="9">
         <v>2837.2323513031001</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="9">
         <v>30</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="9">
         <v>0.72829622479171996</v>
       </c>
       <c r="F36" s="9">
@@ -5095,24 +5086,24 @@
       <c r="V36">
         <v>0.91556490591203998</v>
       </c>
-      <c r="AE36" s="11">
+      <c r="AE36" s="9">
         <v>101.66144371033</v>
       </c>
-      <c r="AF36" s="11">
+      <c r="AF36" s="9">
         <v>31</v>
       </c>
-      <c r="AG36" s="11">
+      <c r="AG36" s="9">
         <v>0.86226895984266005</v>
       </c>
     </row>
     <row r="37" spans="1:33">
-      <c r="A37" s="12">
+      <c r="A37" s="9">
         <v>2804.0144443511999</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="9">
         <v>31</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="9">
         <v>0.67722219070848999</v>
       </c>
       <c r="F37" s="9">
@@ -5151,24 +5142,24 @@
       <c r="V37">
         <v>0.90386546184739003</v>
       </c>
-      <c r="AE37" s="11">
+      <c r="AE37" s="9">
         <v>103.80172729492</v>
       </c>
-      <c r="AF37" s="11">
+      <c r="AF37" s="9">
         <v>32</v>
       </c>
-      <c r="AG37" s="11">
+      <c r="AG37" s="9">
         <v>0.75798210921189002</v>
       </c>
     </row>
     <row r="38" spans="1:33">
-      <c r="A38" s="12">
+      <c r="A38" s="9">
         <v>2864.7305965423998</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="9">
         <v>32</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="9">
         <v>0.83222304658517998</v>
       </c>
       <c r="F38" s="9">
@@ -5207,24 +5198,24 @@
       <c r="V38">
         <v>0.91960307440961997</v>
       </c>
-      <c r="AE38" s="11">
+      <c r="AE38" s="9">
         <v>101.38940811157001</v>
       </c>
-      <c r="AF38" s="11">
+      <c r="AF38" s="9">
         <v>33</v>
       </c>
-      <c r="AG38" s="11">
+      <c r="AG38" s="9">
         <v>0.84985638158358001</v>
       </c>
     </row>
     <row r="39" spans="1:33">
-      <c r="A39" s="12">
+      <c r="A39" s="9">
         <v>2906.5821170806998</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="9">
         <v>33</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="9">
         <v>0.84824966649361999</v>
       </c>
       <c r="F39" s="9">
@@ -5263,24 +5254,24 @@
       <c r="V39">
         <v>0.93549629030257997</v>
       </c>
-      <c r="AE39" s="11">
+      <c r="AE39" s="9">
         <v>103.84297370911</v>
       </c>
-      <c r="AF39" s="11">
+      <c r="AF39" s="9">
         <v>34</v>
       </c>
-      <c r="AG39" s="11">
+      <c r="AG39" s="9">
         <v>0.85838066224760001</v>
       </c>
     </row>
     <row r="40" spans="1:33">
-      <c r="A40" s="12">
+      <c r="A40" s="9">
         <v>2849.8759269714001</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="9">
         <v>34</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="9">
         <v>0.81627044824100004</v>
       </c>
       <c r="F40" s="9">
@@ -5319,24 +5310,24 @@
       <c r="V40">
         <v>0.85381256691648999</v>
       </c>
-      <c r="AE40" s="11">
+      <c r="AE40" s="9">
         <v>101.71318054199</v>
       </c>
-      <c r="AF40" s="11">
+      <c r="AF40" s="9">
         <v>35</v>
       </c>
-      <c r="AG40" s="11">
+      <c r="AG40" s="9">
         <v>0.83348250637631005</v>
       </c>
     </row>
     <row r="41" spans="1:33">
-      <c r="A41" s="12">
+      <c r="A41" s="9">
         <v>2846.6222286224001</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="9">
         <v>35</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="9">
         <v>0.74053295932678997</v>
       </c>
       <c r="F41" s="9">
@@ -5375,24 +5366,24 @@
       <c r="V41">
         <v>0.90648927549654001</v>
       </c>
-      <c r="AE41" s="11">
+      <c r="AE41" s="9">
         <v>103.54900360107</v>
       </c>
-      <c r="AF41" s="11">
+      <c r="AF41" s="9">
         <v>36</v>
       </c>
-      <c r="AG41" s="11">
+      <c r="AG41" s="9">
         <v>0.82719103427067997</v>
       </c>
     </row>
     <row r="42" spans="1:33">
-      <c r="A42" s="12">
+      <c r="A42" s="9">
         <v>2794.9330806732</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="9">
         <v>36</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="9">
         <v>0.85305807300895997</v>
       </c>
       <c r="F42" s="9">
@@ -5431,24 +5422,24 @@
       <c r="V42">
         <v>0.92656902916953998</v>
       </c>
-      <c r="AE42" s="11">
+      <c r="AE42" s="9">
         <v>101.57012939453</v>
       </c>
-      <c r="AF42" s="11">
+      <c r="AF42" s="9">
         <v>37</v>
       </c>
-      <c r="AG42" s="11">
+      <c r="AG42" s="9">
         <v>0.83088226657112996</v>
       </c>
     </row>
     <row r="43" spans="1:33">
-      <c r="A43" s="12">
+      <c r="A43" s="9">
         <v>2864.9783134459999</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="9">
         <v>37</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="9">
         <v>0.82831335936893002</v>
       </c>
       <c r="F43" s="9">
@@ -5487,24 +5478,24 @@
       <c r="V43">
         <v>0.89216916836962001</v>
       </c>
-      <c r="AE43" s="11">
+      <c r="AE43" s="9">
         <v>105.93724250792999</v>
       </c>
-      <c r="AF43" s="11">
+      <c r="AF43" s="9">
         <v>38</v>
       </c>
-      <c r="AG43" s="11">
+      <c r="AG43" s="9">
         <v>0.83852718849061003</v>
       </c>
     </row>
     <row r="44" spans="1:33">
-      <c r="A44" s="12">
+      <c r="A44" s="9">
         <v>3334.1064453125</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="9">
         <v>38</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="9">
         <v>0.79959619323917996</v>
       </c>
       <c r="F44" s="9">
@@ -5543,27 +5534,27 @@
       <c r="V44">
         <v>0.90177573670111</v>
       </c>
-      <c r="Y44" s="13" t="s">
+      <c r="Y44" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AE44" s="11">
+      <c r="AE44" s="9">
         <v>101.72080993652</v>
       </c>
-      <c r="AF44" s="11">
+      <c r="AF44" s="9">
         <v>39</v>
       </c>
-      <c r="AG44" s="11">
+      <c r="AG44" s="9">
         <v>0.78702200610026996</v>
       </c>
     </row>
     <row r="45" spans="1:33">
-      <c r="A45" s="12">
+      <c r="A45" s="9">
         <v>3004.7950744629002</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="9">
         <v>39</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="9">
         <v>0.85098132371163004</v>
       </c>
       <c r="F45" s="9">
@@ -5602,7 +5593,7 @@
       <c r="V45">
         <v>0.90299634835676001</v>
       </c>
-      <c r="Y45" s="14">
+      <c r="Y45" s="12">
         <v>0.05</v>
       </c>
       <c r="Z45" cm="1">
@@ -5621,24 +5612,24 @@
         <f>AB45/75*0.05</f>
         <v>0</v>
       </c>
-      <c r="AE45" s="11">
+      <c r="AE45" s="9">
         <v>103.50513458252</v>
       </c>
-      <c r="AF45" s="11">
+      <c r="AF45" s="9">
         <v>40</v>
       </c>
-      <c r="AG45" s="11">
+      <c r="AG45" s="9">
         <v>0.81470877858419</v>
       </c>
     </row>
     <row r="46" spans="1:33">
-      <c r="A46" s="12">
+      <c r="A46" s="9">
         <v>2752.0980834961001</v>
       </c>
-      <c r="B46" s="12">
+      <c r="B46" s="9">
         <v>40</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="9">
         <v>0.82869492347726004</v>
       </c>
       <c r="F46" s="9">
@@ -5677,7 +5668,7 @@
       <c r="V46">
         <v>0.90279686416166005</v>
       </c>
-      <c r="Y46" s="14">
+      <c r="Y46" s="12">
         <v>0.1</v>
       </c>
       <c r="Z46">
@@ -5694,24 +5685,24 @@
         <f t="shared" ref="AC46:AC65" si="1">AB46/75*0.05</f>
         <v>0</v>
       </c>
-      <c r="AE46" s="11">
+      <c r="AE46" s="9">
         <v>101.43184661865</v>
       </c>
-      <c r="AF46" s="11">
+      <c r="AF46" s="9">
         <v>41</v>
       </c>
-      <c r="AG46" s="11">
+      <c r="AG46" s="9">
         <v>0.85015760336927004</v>
       </c>
     </row>
     <row r="47" spans="1:33">
-      <c r="A47" s="12">
+      <c r="A47" s="9">
         <v>2712.2099399567001</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B47" s="9">
         <v>41</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="9">
         <v>0.71886833745614998</v>
       </c>
       <c r="F47" s="9">
@@ -5750,7 +5741,7 @@
       <c r="V47">
         <v>0.88450018243065998</v>
       </c>
-      <c r="Y47" s="14">
+      <c r="Y47" s="12">
         <v>0.15</v>
       </c>
       <c r="Z47">
@@ -5767,24 +5758,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE47" s="11">
+      <c r="AE47" s="9">
         <v>103.102684021</v>
       </c>
-      <c r="AF47" s="11">
+      <c r="AF47" s="9">
         <v>42</v>
       </c>
-      <c r="AG47" s="11">
+      <c r="AG47" s="9">
         <v>0.83724517990911995</v>
       </c>
     </row>
     <row r="48" spans="1:33">
-      <c r="A48" s="12">
+      <c r="A48" s="9">
         <v>3080.4755687714</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="9">
         <v>42</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="9">
         <v>0.73773829633205001</v>
       </c>
       <c r="F48" s="9">
@@ -5823,7 +5814,7 @@
       <c r="V48">
         <v>0.86992349432104998</v>
       </c>
-      <c r="Y48" s="14">
+      <c r="Y48" s="12">
         <v>0.2</v>
       </c>
       <c r="Z48">
@@ -5840,24 +5831,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE48" s="11">
+      <c r="AE48" s="9">
         <v>104.66051101684999</v>
       </c>
-      <c r="AF48" s="11">
+      <c r="AF48" s="9">
         <v>43</v>
       </c>
-      <c r="AG48" s="11">
+      <c r="AG48" s="9">
         <v>0.69999930816434996</v>
       </c>
     </row>
     <row r="49" spans="1:33">
-      <c r="A49" s="12">
+      <c r="A49" s="9">
         <v>2829.1056156158002</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="9">
         <v>43</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="9">
         <v>0.69836285303973</v>
       </c>
       <c r="F49" s="9">
@@ -5896,7 +5887,7 @@
       <c r="V49">
         <v>0.92135362989744995</v>
       </c>
-      <c r="Y49" s="14">
+      <c r="Y49" s="12">
         <v>0.25</v>
       </c>
       <c r="Z49">
@@ -5913,24 +5904,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE49" s="11">
+      <c r="AE49" s="9">
         <v>103.48963737488</v>
       </c>
-      <c r="AF49" s="11">
+      <c r="AF49" s="9">
         <v>44</v>
       </c>
-      <c r="AG49" s="11">
+      <c r="AG49" s="9">
         <v>0.86705713804146001</v>
       </c>
     </row>
     <row r="50" spans="1:33">
-      <c r="A50" s="12">
+      <c r="A50" s="9">
         <v>2671.1637973785</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="9">
         <v>44</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="9">
         <v>0.82702507232401001</v>
       </c>
       <c r="F50" s="9">
@@ -5969,7 +5960,7 @@
       <c r="V50">
         <v>0.92735212662802002</v>
       </c>
-      <c r="Y50" s="14">
+      <c r="Y50" s="12">
         <v>0.3</v>
       </c>
       <c r="Z50">
@@ -5986,24 +5977,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE50" s="11">
+      <c r="AE50" s="9">
         <v>101.31072998047</v>
       </c>
-      <c r="AF50" s="11">
+      <c r="AF50" s="9">
         <v>45</v>
       </c>
-      <c r="AG50" s="11">
+      <c r="AG50" s="9">
         <v>0.84913307613852995</v>
       </c>
     </row>
     <row r="51" spans="1:33">
-      <c r="A51" s="12">
+      <c r="A51" s="9">
         <v>2707.1595191955998</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="9">
         <v>45</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="9">
         <v>0.84025798998845003</v>
       </c>
       <c r="F51" s="9">
@@ -6042,7 +6033,7 @@
       <c r="V51">
         <v>0.92592415383585003</v>
       </c>
-      <c r="Y51" s="14">
+      <c r="Y51" s="12">
         <v>0.35</v>
       </c>
       <c r="Z51">
@@ -6059,24 +6050,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE51" s="11">
+      <c r="AE51" s="9">
         <v>101.52077674866</v>
       </c>
-      <c r="AF51" s="11">
+      <c r="AF51" s="9">
         <v>46</v>
       </c>
-      <c r="AG51" s="11">
+      <c r="AG51" s="9">
         <v>0.86022470239674997</v>
       </c>
     </row>
     <row r="52" spans="1:33">
-      <c r="A52" s="12">
+      <c r="A52" s="9">
         <v>2829.6802043915</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="9">
         <v>46</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="9">
         <v>0.86236503998559</v>
       </c>
       <c r="F52" s="9">
@@ -6115,7 +6106,7 @@
       <c r="V52">
         <v>0.92405995219095005</v>
       </c>
-      <c r="Y52" s="14">
+      <c r="Y52" s="12">
         <v>0.4</v>
       </c>
       <c r="Z52">
@@ -6132,24 +6123,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE52" s="11">
+      <c r="AE52" s="9">
         <v>102.4534702301</v>
       </c>
-      <c r="AF52" s="11">
+      <c r="AF52" s="9">
         <v>47</v>
       </c>
-      <c r="AG52" s="11">
+      <c r="AG52" s="9">
         <v>0.85703923676890004</v>
       </c>
     </row>
     <row r="53" spans="1:33">
-      <c r="A53" s="12">
+      <c r="A53" s="9">
         <v>2682.4929714202999</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="9">
         <v>47</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="9">
         <v>0.83478902039481995</v>
       </c>
       <c r="F53" s="9">
@@ -6188,7 +6179,7 @@
       <c r="V53">
         <v>0.88629348529134999</v>
       </c>
-      <c r="Y53" s="14">
+      <c r="Y53" s="12">
         <v>0.45</v>
       </c>
       <c r="Z53">
@@ -6205,24 +6196,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE53" s="11">
+      <c r="AE53" s="9">
         <v>101.41086578369</v>
       </c>
-      <c r="AF53" s="11">
+      <c r="AF53" s="9">
         <v>48</v>
       </c>
-      <c r="AG53" s="11">
+      <c r="AG53" s="9">
         <v>0.84722511779177001</v>
       </c>
     </row>
     <row r="54" spans="1:33">
-      <c r="A54" s="12">
+      <c r="A54" s="9">
         <v>2631.8764686584</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="9">
         <v>48</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="9">
         <v>0.81930815739914997</v>
       </c>
       <c r="F54" s="9">
@@ -6261,7 +6252,7 @@
       <c r="V54">
         <v>0.93198923629607999</v>
       </c>
-      <c r="Y54" s="14">
+      <c r="Y54" s="12">
         <v>0.5</v>
       </c>
       <c r="Z54">
@@ -6278,24 +6269,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE54" s="11">
+      <c r="AE54" s="9">
         <v>101.82213783264</v>
       </c>
-      <c r="AF54" s="11">
+      <c r="AF54" s="9">
         <v>49</v>
       </c>
-      <c r="AG54" s="11">
+      <c r="AG54" s="9">
         <v>0.79352353652527996</v>
       </c>
     </row>
     <row r="55" spans="1:33">
-      <c r="A55" s="12">
+      <c r="A55" s="9">
         <v>2996.9894886017</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="9">
         <v>49</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="9">
         <v>0.82831288368633005</v>
       </c>
       <c r="F55" s="9">
@@ -6334,7 +6325,7 @@
       <c r="V55">
         <v>0.92017103342050999</v>
       </c>
-      <c r="Y55" s="14">
+      <c r="Y55" s="12">
         <v>0.55000000000000004</v>
       </c>
       <c r="Z55">
@@ -6351,24 +6342,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE55" s="11">
+      <c r="AE55" s="9">
         <v>103.57403755188</v>
       </c>
-      <c r="AF55" s="11">
+      <c r="AF55" s="9">
         <v>50</v>
       </c>
-      <c r="AG55" s="11">
+      <c r="AG55" s="9">
         <v>0.84220630809080999</v>
       </c>
     </row>
     <row r="56" spans="1:33">
-      <c r="A56" s="12">
+      <c r="A56" s="9">
         <v>3620.4750537872001</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B56" s="9">
         <v>50</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="9">
         <v>0.83565909752950995</v>
       </c>
       <c r="F56" s="9">
@@ -6407,7 +6398,7 @@
       <c r="V56">
         <v>0.90959947545374997</v>
       </c>
-      <c r="Y56" s="14">
+      <c r="Y56" s="12">
         <v>0.6</v>
       </c>
       <c r="Z56">
@@ -6424,24 +6415,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE56" s="11">
+      <c r="AE56" s="9">
         <v>101.02701187133999</v>
       </c>
-      <c r="AF56" s="11">
+      <c r="AF56" s="9">
         <v>51</v>
       </c>
-      <c r="AG56" s="11">
+      <c r="AG56" s="9">
         <v>0.85478912040913002</v>
       </c>
     </row>
     <row r="57" spans="1:33">
-      <c r="A57" s="12">
+      <c r="A57" s="9">
         <v>4173.3121871947997</v>
       </c>
-      <c r="B57" s="12">
+      <c r="B57" s="9">
         <v>51</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="9">
         <v>0.82714252941369004</v>
       </c>
       <c r="F57" s="9">
@@ -6480,7 +6471,7 @@
       <c r="V57">
         <v>0.90001012555690996</v>
       </c>
-      <c r="Y57" s="14">
+      <c r="Y57" s="12">
         <v>0.65</v>
       </c>
       <c r="Z57">
@@ -6497,24 +6488,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE57" s="11">
+      <c r="AE57" s="9">
         <v>101.637840271</v>
       </c>
-      <c r="AF57" s="11">
+      <c r="AF57" s="9">
         <v>52</v>
       </c>
-      <c r="AG57" s="11">
+      <c r="AG57" s="9">
         <v>0.70945686081791004</v>
       </c>
     </row>
     <row r="58" spans="1:33">
-      <c r="A58" s="12">
+      <c r="A58" s="9">
         <v>5991.2035465239996</v>
       </c>
-      <c r="B58" s="12">
+      <c r="B58" s="9">
         <v>52</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="9">
         <v>0.84099916656174001</v>
       </c>
       <c r="F58" s="9">
@@ -6553,7 +6544,7 @@
       <c r="V58">
         <v>0.93037776827141005</v>
       </c>
-      <c r="Y58" s="14">
+      <c r="Y58" s="12">
         <v>0.7</v>
       </c>
       <c r="Z58">
@@ -6570,24 +6561,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE58" s="11">
+      <c r="AE58" s="9">
         <v>101.65047645569</v>
       </c>
-      <c r="AF58" s="11">
+      <c r="AF58" s="9">
         <v>53</v>
       </c>
-      <c r="AG58" s="11">
+      <c r="AG58" s="9">
         <v>0.83411882383685998</v>
       </c>
     </row>
     <row r="59" spans="1:33">
-      <c r="A59" s="12">
+      <c r="A59" s="9">
         <v>3401.3302326202001</v>
       </c>
-      <c r="B59" s="12">
+      <c r="B59" s="9">
         <v>53</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="9">
         <v>0.83907694713127001</v>
       </c>
       <c r="F59" s="9">
@@ -6626,7 +6617,7 @@
       <c r="V59">
         <v>0.90249035742996997</v>
       </c>
-      <c r="Y59" s="14">
+      <c r="Y59" s="12">
         <v>0.75</v>
       </c>
       <c r="Z59">
@@ -6643,24 +6634,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE59" s="11">
+      <c r="AE59" s="9">
         <v>101.72796249389999</v>
       </c>
-      <c r="AF59" s="11">
+      <c r="AF59" s="9">
         <v>54</v>
       </c>
-      <c r="AG59" s="11">
+      <c r="AG59" s="9">
         <v>0.83832340396723004</v>
       </c>
     </row>
     <row r="60" spans="1:33">
-      <c r="A60" s="12">
+      <c r="A60" s="9">
         <v>3303.1659126282002</v>
       </c>
-      <c r="B60" s="12">
+      <c r="B60" s="9">
         <v>54</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="9">
         <v>0.85326167862566005</v>
       </c>
       <c r="F60" s="9">
@@ -6699,7 +6690,7 @@
       <c r="V60">
         <v>0.91551357294835001</v>
       </c>
-      <c r="Y60" s="14">
+      <c r="Y60" s="12">
         <v>0.8</v>
       </c>
       <c r="Z60">
@@ -6716,24 +6707,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE60" s="11">
+      <c r="AE60" s="9">
         <v>101.12023353577</v>
       </c>
-      <c r="AF60" s="11">
+      <c r="AF60" s="9">
         <v>55</v>
       </c>
-      <c r="AG60" s="11">
+      <c r="AG60" s="9">
         <v>0.78689007368505004</v>
       </c>
     </row>
     <row r="61" spans="1:33">
-      <c r="A61" s="12">
+      <c r="A61" s="9">
         <v>3662.1420383453001</v>
       </c>
-      <c r="B61" s="12">
+      <c r="B61" s="9">
         <v>55</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="9">
         <v>0.83511323073321997</v>
       </c>
       <c r="F61" s="9">
@@ -6772,7 +6763,7 @@
       <c r="V61">
         <v>0.93911348860695998</v>
       </c>
-      <c r="Y61" s="14">
+      <c r="Y61" s="12">
         <v>0.85</v>
       </c>
       <c r="Z61">
@@ -6789,24 +6780,24 @@
         <f t="shared" si="1"/>
         <v>1.3333333333333335E-3</v>
       </c>
-      <c r="AE61" s="11">
+      <c r="AE61" s="9">
         <v>101.81379318237001</v>
       </c>
-      <c r="AF61" s="11">
+      <c r="AF61" s="9">
         <v>56</v>
       </c>
-      <c r="AG61" s="11">
+      <c r="AG61" s="9">
         <v>0.84946093339549</v>
       </c>
     </row>
     <row r="62" spans="1:33">
-      <c r="A62" s="12">
+      <c r="A62" s="9">
         <v>4017.8256034851001</v>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="9">
         <v>56</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="9">
         <v>0.83395282827600004</v>
       </c>
       <c r="F62" s="9">
@@ -6845,7 +6836,7 @@
       <c r="V62">
         <v>0.90336239622878001</v>
       </c>
-      <c r="Y62" s="14">
+      <c r="Y62" s="12">
         <v>0.9</v>
       </c>
       <c r="Z62">
@@ -6862,24 +6853,24 @@
         <f t="shared" si="1"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AE62" s="11">
+      <c r="AE62" s="9">
         <v>102.10251808167</v>
       </c>
-      <c r="AF62" s="11">
+      <c r="AF62" s="9">
         <v>57</v>
       </c>
-      <c r="AG62" s="11">
+      <c r="AG62" s="9">
         <v>0.83245597580135</v>
       </c>
     </row>
     <row r="63" spans="1:33">
-      <c r="A63" s="12">
+      <c r="A63" s="9">
         <v>3553.5860061645999</v>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="9">
         <v>57</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="9">
         <v>0.75460240470447004</v>
       </c>
       <c r="F63" s="9">
@@ -6918,7 +6909,7 @@
       <c r="V63">
         <v>0.92335763267352999</v>
       </c>
-      <c r="Y63" s="14">
+      <c r="Y63" s="12">
         <v>0.95</v>
       </c>
       <c r="Z63">
@@ -6935,24 +6926,24 @@
         <f t="shared" si="1"/>
         <v>4.066666666666667E-2</v>
       </c>
-      <c r="AE63" s="11">
+      <c r="AE63" s="9">
         <v>103.6012172699</v>
       </c>
-      <c r="AF63" s="11">
+      <c r="AF63" s="9">
         <v>58</v>
       </c>
-      <c r="AG63" s="11">
+      <c r="AG63" s="9">
         <v>0.84730358805413997</v>
       </c>
     </row>
     <row r="64" spans="1:33">
-      <c r="A64" s="12">
+      <c r="A64" s="9">
         <v>3238.067150116</v>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="9">
         <v>58</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="9">
         <v>0.81876721541026998</v>
       </c>
       <c r="F64" s="9">
@@ -6991,7 +6982,7 @@
       <c r="V64">
         <v>0.90007053023372996</v>
       </c>
-      <c r="Y64" s="14">
+      <c r="Y64" s="12">
         <v>1</v>
       </c>
       <c r="Z64">
@@ -7008,24 +6999,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE64" s="11">
+      <c r="AE64" s="9">
         <v>101.68671607971</v>
       </c>
-      <c r="AF64" s="11">
+      <c r="AF64" s="9">
         <v>59</v>
       </c>
-      <c r="AG64" s="11">
+      <c r="AG64" s="9">
         <v>0.85014250955856996</v>
       </c>
     </row>
     <row r="65" spans="1:33">
-      <c r="A65" s="12">
+      <c r="A65" s="9">
         <v>2862.5309467316001</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="9">
         <v>59</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="9">
         <v>0.82434561233244996</v>
       </c>
       <c r="F65" s="9">
@@ -7064,7 +7055,7 @@
       <c r="V65">
         <v>0.91170859045079999</v>
       </c>
-      <c r="Y65" s="14"/>
+      <c r="Y65" s="12"/>
       <c r="Z65">
         <v>0</v>
       </c>
@@ -7075,24 +7066,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE65" s="11">
+      <c r="AE65" s="9">
         <v>104.08639907836999</v>
       </c>
-      <c r="AF65" s="11">
+      <c r="AF65" s="9">
         <v>60</v>
       </c>
-      <c r="AG65" s="11">
+      <c r="AG65" s="9">
         <v>0.70596803528028995</v>
       </c>
     </row>
     <row r="66" spans="1:33">
-      <c r="A66" s="12">
+      <c r="A66" s="9">
         <v>2927.4230003357002</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="9">
         <v>60</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="9">
         <v>0.83480180196479004</v>
       </c>
       <c r="F66" s="9">
@@ -7131,25 +7122,25 @@
       <c r="V66">
         <v>0.91062429432985004</v>
       </c>
-      <c r="Y66" s="14"/>
-      <c r="AE66" s="11">
+      <c r="Y66" s="12"/>
+      <c r="AE66" s="9">
         <v>101.37581825255999</v>
       </c>
-      <c r="AF66" s="11">
+      <c r="AF66" s="9">
         <v>61</v>
       </c>
-      <c r="AG66" s="11">
+      <c r="AG66" s="9">
         <v>0.81679781509423999</v>
       </c>
     </row>
     <row r="67" spans="1:33">
-      <c r="A67" s="12">
+      <c r="A67" s="9">
         <v>2793.2739257812</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="9">
         <v>61</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="9">
         <v>0.83885986423570003</v>
       </c>
       <c r="F67" s="9">
@@ -7188,25 +7179,25 @@
       <c r="V67">
         <v>0.87914196415857004</v>
       </c>
-      <c r="Y67" s="14"/>
-      <c r="AE67" s="11">
+      <c r="Y67" s="12"/>
+      <c r="AE67" s="9">
         <v>101.99284553528</v>
       </c>
-      <c r="AF67" s="11">
+      <c r="AF67" s="9">
         <v>62</v>
       </c>
-      <c r="AG67" s="11">
+      <c r="AG67" s="9">
         <v>0.84169218989280004</v>
       </c>
     </row>
     <row r="68" spans="1:33">
-      <c r="A68" s="12">
+      <c r="A68" s="9">
         <v>2847.7237224578998</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="9">
         <v>62</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="9">
         <v>0.83724312860049999</v>
       </c>
       <c r="F68" s="9">
@@ -7245,24 +7236,24 @@
       <c r="V68">
         <v>0.92995273208546003</v>
       </c>
-      <c r="AE68" s="11">
+      <c r="AE68" s="9">
         <v>101.73463821411001</v>
       </c>
-      <c r="AF68" s="11">
+      <c r="AF68" s="9">
         <v>63</v>
       </c>
-      <c r="AG68" s="11">
+      <c r="AG68" s="9">
         <v>0.82693441139602997</v>
       </c>
     </row>
     <row r="69" spans="1:33">
-      <c r="A69" s="12">
+      <c r="A69" s="9">
         <v>2867.7041530608999</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="9">
         <v>63</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="9">
         <v>0.83619916700411001</v>
       </c>
       <c r="F69" s="9">
@@ -7301,24 +7292,24 @@
       <c r="V69">
         <v>0.91618264482585998</v>
       </c>
-      <c r="AE69" s="11">
+      <c r="AE69" s="9">
         <v>101.47285461426</v>
       </c>
-      <c r="AF69" s="11">
+      <c r="AF69" s="9">
         <v>64</v>
       </c>
-      <c r="AG69" s="11">
+      <c r="AG69" s="9">
         <v>0.83817892784598003</v>
       </c>
     </row>
     <row r="70" spans="1:33">
-      <c r="A70" s="12">
+      <c r="A70" s="9">
         <v>2832.3373794556001</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="9">
         <v>64</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="9">
         <v>0.80824883786228996</v>
       </c>
       <c r="F70" s="9">
@@ -7357,24 +7348,24 @@
       <c r="V70">
         <v>0.91536785994533998</v>
       </c>
-      <c r="AE70" s="11">
+      <c r="AE70" s="9">
         <v>101.84454917908</v>
       </c>
-      <c r="AF70" s="11">
+      <c r="AF70" s="9">
         <v>65</v>
       </c>
-      <c r="AG70" s="11">
+      <c r="AG70" s="9">
         <v>0.75067790724308003</v>
       </c>
     </row>
     <row r="71" spans="1:33">
-      <c r="A71" s="12">
+      <c r="A71" s="9">
         <v>2856.5959930419999</v>
       </c>
-      <c r="B71" s="12">
+      <c r="B71" s="9">
         <v>65</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="9">
         <v>0.84013032853652003</v>
       </c>
       <c r="F71" s="9">
@@ -7413,24 +7404,24 @@
       <c r="V71">
         <v>0.92537977320585996</v>
       </c>
-      <c r="AE71" s="11">
+      <c r="AE71" s="9">
         <v>102.9634475708</v>
       </c>
-      <c r="AF71" s="11">
+      <c r="AF71" s="9">
         <v>66</v>
       </c>
-      <c r="AG71" s="11">
+      <c r="AG71" s="9">
         <v>0.86007280866661995</v>
       </c>
     </row>
     <row r="72" spans="1:33">
-      <c r="A72" s="12">
+      <c r="A72" s="9">
         <v>2957.8514099120998</v>
       </c>
-      <c r="B72" s="12">
+      <c r="B72" s="9">
         <v>66</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="9">
         <v>0.78345511600080997</v>
       </c>
       <c r="F72" s="9">
@@ -7469,24 +7460,24 @@
       <c r="V72">
         <v>0.89761131157443996</v>
       </c>
-      <c r="AE72" s="11">
+      <c r="AE72" s="9">
         <v>101.95827484131</v>
       </c>
-      <c r="AF72" s="11">
+      <c r="AF72" s="9">
         <v>67</v>
       </c>
-      <c r="AG72" s="11">
+      <c r="AG72" s="9">
         <v>0.84532118850714</v>
       </c>
     </row>
     <row r="73" spans="1:33">
-      <c r="A73" s="12">
+      <c r="A73" s="9">
         <v>3104.2642593383998</v>
       </c>
-      <c r="B73" s="12">
+      <c r="B73" s="9">
         <v>67</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="9">
         <v>0.84226174345950999</v>
       </c>
       <c r="F73" s="9">
@@ -7525,24 +7516,24 @@
       <c r="V73">
         <v>0.93327641477519996</v>
       </c>
-      <c r="AE73" s="11">
+      <c r="AE73" s="9">
         <v>101.35149955750001</v>
       </c>
-      <c r="AF73" s="11">
+      <c r="AF73" s="9">
         <v>68</v>
       </c>
-      <c r="AG73" s="11">
+      <c r="AG73" s="9">
         <v>0.81390014527105004</v>
       </c>
     </row>
     <row r="74" spans="1:33">
-      <c r="A74" s="12">
+      <c r="A74" s="9">
         <v>3015.0809288024998</v>
       </c>
-      <c r="B74" s="12">
+      <c r="B74" s="9">
         <v>68</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="9">
         <v>0.80540705243622002</v>
       </c>
       <c r="F74" s="9">
@@ -7581,24 +7572,24 @@
       <c r="V74">
         <v>0.84873148280237998</v>
       </c>
-      <c r="AE74" s="11">
+      <c r="AE74" s="9">
         <v>101.42493247986</v>
       </c>
-      <c r="AF74" s="11">
+      <c r="AF74" s="9">
         <v>69</v>
       </c>
-      <c r="AG74" s="11">
+      <c r="AG74" s="9">
         <v>0.86024106822429003</v>
       </c>
     </row>
     <row r="75" spans="1:33">
-      <c r="A75" s="12">
+      <c r="A75" s="9">
         <v>2946.5353488922001</v>
       </c>
-      <c r="B75" s="12">
+      <c r="B75" s="9">
         <v>69</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="9">
         <v>0.78589747649052</v>
       </c>
       <c r="F75" s="9">
@@ -7637,24 +7628,24 @@
       <c r="V75">
         <v>0.93636480834240998</v>
       </c>
-      <c r="AE75" s="11">
+      <c r="AE75" s="9">
         <v>103.75714302063</v>
       </c>
-      <c r="AF75" s="11">
+      <c r="AF75" s="9">
         <v>70</v>
       </c>
-      <c r="AG75" s="11">
+      <c r="AG75" s="9">
         <v>0.85067355927563004</v>
       </c>
     </row>
     <row r="76" spans="1:33">
-      <c r="A76" s="12">
+      <c r="A76" s="9">
         <v>2988.8606071472</v>
       </c>
-      <c r="B76" s="12">
+      <c r="B76" s="9">
         <v>70</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="9">
         <v>0.76976342967882005</v>
       </c>
       <c r="F76" s="9">
@@ -7693,24 +7684,24 @@
       <c r="V76">
         <v>0.91260542720938997</v>
       </c>
-      <c r="AE76" s="11">
+      <c r="AE76" s="9">
         <v>101.47500038147</v>
       </c>
-      <c r="AF76" s="11">
+      <c r="AF76" s="9">
         <v>71</v>
       </c>
-      <c r="AG76" s="11">
+      <c r="AG76" s="9">
         <v>0.72695182455276997</v>
       </c>
     </row>
     <row r="77" spans="1:33">
-      <c r="A77" s="12">
+      <c r="A77" s="9">
         <v>3009.0124607086</v>
       </c>
-      <c r="B77" s="12">
+      <c r="B77" s="9">
         <v>71</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="9">
         <v>0.83498814530854004</v>
       </c>
       <c r="F77" s="9">
@@ -7749,24 +7740,24 @@
       <c r="V77">
         <v>0.92486829181176999</v>
       </c>
-      <c r="AE77" s="11">
+      <c r="AE77" s="9">
         <v>103.35016250610001</v>
       </c>
-      <c r="AF77" s="11">
+      <c r="AF77" s="9">
         <v>72</v>
       </c>
-      <c r="AG77" s="11">
+      <c r="AG77" s="9">
         <v>0.81076152484927999</v>
       </c>
     </row>
     <row r="78" spans="1:33">
-      <c r="A78" s="12">
+      <c r="A78" s="9">
         <v>3086.5390300751001</v>
       </c>
-      <c r="B78" s="12">
+      <c r="B78" s="9">
         <v>72</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="9">
         <v>0.82757691685974</v>
       </c>
       <c r="F78" s="9">
@@ -7805,24 +7796,24 @@
       <c r="V78">
         <v>0.92864822006907</v>
       </c>
-      <c r="AE78" s="11">
+      <c r="AE78" s="9">
         <v>101.68695449829001</v>
       </c>
-      <c r="AF78" s="11">
+      <c r="AF78" s="9">
         <v>73</v>
       </c>
-      <c r="AG78" s="11">
+      <c r="AG78" s="9">
         <v>0.82164096752064997</v>
       </c>
     </row>
     <row r="79" spans="1:33">
-      <c r="A79" s="12">
+      <c r="A79" s="9">
         <v>3037.5897884369001</v>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="9">
         <v>73</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="9">
         <v>0.85860322504562003</v>
       </c>
       <c r="F79" s="9">
@@ -7861,24 +7852,24 @@
       <c r="V79">
         <v>0.93419152336754996</v>
       </c>
-      <c r="AE79" s="11">
+      <c r="AE79" s="9">
         <v>101.44352912903</v>
       </c>
-      <c r="AF79" s="11">
+      <c r="AF79" s="9">
         <v>74</v>
       </c>
-      <c r="AG79" s="11">
+      <c r="AG79" s="9">
         <v>0.78984896784585001</v>
       </c>
     </row>
     <row r="80" spans="1:33">
-      <c r="A80" s="12">
+      <c r="A80" s="9">
         <v>2989.9842739105002</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="9">
         <v>74</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="9">
         <v>0.79477492073690004</v>
       </c>
       <c r="F80" s="9">
